--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MELILLA CIUDAD DEL DEPORTE ENRIQUE SOLER.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MELILLA CIUDAD DEL DEPORTE ENRIQUE SOLER.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>112.6973</v>
+        <v>77.616</v>
       </c>
       <c r="E2" t="n">
-        <v>89.9387</v>
+        <v>64.03360000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>22.758</v>
+        <v>13.5824</v>
       </c>
       <c r="G2" t="n">
         <v>40.8599</v>
@@ -610,13 +610,13 @@
         <v>64.8189</v>
       </c>
       <c r="S2" t="n">
-        <v>60.6752</v>
+        <v>25.594</v>
       </c>
       <c r="T2" t="n">
-        <v>42.7171</v>
+        <v>16.8116</v>
       </c>
       <c r="U2" t="n">
-        <v>17.9583</v>
+        <v>8.782399999999999</v>
       </c>
       <c r="V2" t="n">
         <v>4.4223</v>
@@ -643,13 +643,13 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>22.1347</v>
+        <v>38.1285</v>
       </c>
       <c r="E3" t="n">
-        <v>20.9067</v>
+        <v>30.4454</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2282</v>
+        <v>7.682899999999999</v>
       </c>
       <c r="G3" t="n">
         <v>-1.8338</v>
@@ -688,13 +688,13 @@
         <v>52.7275</v>
       </c>
       <c r="S3" t="n">
-        <v>-16.3685</v>
+        <v>-0.3747</v>
       </c>
       <c r="T3" t="n">
-        <v>-6.721100000000001</v>
+        <v>2.8178</v>
       </c>
       <c r="U3" t="n">
-        <v>-9.6473</v>
+        <v>-3.1925</v>
       </c>
       <c r="V3" t="n">
         <v>10.2071</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CERISUELO QUESADA</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>14.066</v>
+        <v>27.4048</v>
       </c>
       <c r="E4" t="n">
-        <v>7.9972</v>
+        <v>30.2172</v>
       </c>
       <c r="F4" t="n">
-        <v>6.0687</v>
+        <v>-2.8122</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.2803</v>
+        <v>32.2746</v>
       </c>
       <c r="H4" t="n">
-        <v>-12.3991</v>
+        <v>-1.0315</v>
       </c>
       <c r="I4" t="n">
-        <v>8.1188</v>
+        <v>33.3062</v>
       </c>
       <c r="J4" t="n">
-        <v>23.8739</v>
+        <v>62.2445</v>
       </c>
       <c r="K4" t="n">
-        <v>13.0987</v>
+        <v>23.7128</v>
       </c>
       <c r="L4" t="n">
-        <v>10.7754</v>
+        <v>38.532</v>
       </c>
       <c r="M4" t="n">
-        <v>-28.1542</v>
+        <v>-29.9698</v>
       </c>
       <c r="N4" t="n">
-        <v>-25.4978</v>
+        <v>-24.744</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.6564</v>
+        <v>-5.2256</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.3522</v>
+        <v>-2.1804</v>
       </c>
       <c r="Q4" t="n">
-        <v>-47.3749</v>
+        <v>-44.2035</v>
       </c>
       <c r="R4" t="n">
-        <v>42.0235</v>
+        <v>42.0236</v>
       </c>
       <c r="S4" t="n">
-        <v>20.9488</v>
+        <v>-2.0443</v>
       </c>
       <c r="T4" t="n">
-        <v>11.5156</v>
+        <v>0.5129</v>
       </c>
       <c r="U4" t="n">
-        <v>9.433199999999999</v>
+        <v>-2.5573</v>
       </c>
       <c r="V4" t="n">
-        <v>2.7495</v>
+        <v>-0.645</v>
       </c>
       <c r="W4" t="n">
-        <v>19.9828</v>
+        <v>11.6638</v>
       </c>
       <c r="X4" t="n">
-        <v>-17.2337</v>
+        <v>-12.3087</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SHERIFF</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>11.7945</v>
+        <v>20.6835</v>
       </c>
       <c r="E5" t="n">
-        <v>7.255999999999999</v>
+        <v>17.2114</v>
       </c>
       <c r="F5" t="n">
-        <v>4.5385</v>
+        <v>3.472000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.540399999999999</v>
+        <v>-7.256</v>
       </c>
       <c r="H5" t="n">
-        <v>-8.1022</v>
+        <v>-6.471499999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>6.5618</v>
+        <v>-0.7843999999999991</v>
       </c>
       <c r="J5" t="n">
-        <v>11.0265</v>
+        <v>25.2594</v>
       </c>
       <c r="K5" t="n">
-        <v>4.835299999999999</v>
+        <v>21.6446</v>
       </c>
       <c r="L5" t="n">
-        <v>6.1914</v>
+        <v>3.6151</v>
       </c>
       <c r="M5" t="n">
-        <v>-12.5666</v>
+        <v>-32.5157</v>
       </c>
       <c r="N5" t="n">
-        <v>-12.9372</v>
+        <v>-28.1163</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3707000000000001</v>
+        <v>-4.399</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1984000000000001</v>
+        <v>21.2099</v>
       </c>
       <c r="Q5" t="n">
-        <v>-36.6709</v>
+        <v>-28.9402</v>
       </c>
       <c r="R5" t="n">
-        <v>36.4732</v>
+        <v>50.1506</v>
       </c>
       <c r="S5" t="n">
-        <v>14.9315</v>
+        <v>2.3198</v>
       </c>
       <c r="T5" t="n">
-        <v>10.755</v>
+        <v>1.6089</v>
       </c>
       <c r="U5" t="n">
-        <v>4.1757</v>
+        <v>0.7109000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.398299999999999</v>
+        <v>4.4098</v>
       </c>
       <c r="W5" t="n">
-        <v>22.1455</v>
+        <v>19.2839</v>
       </c>
       <c r="X5" t="n">
-        <v>-23.5436</v>
+        <v>-14.8737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>J. CERISUELO QUESADA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>6.573900000000001</v>
+        <v>7.404999999999998</v>
       </c>
       <c r="E6" t="n">
-        <v>14.6056</v>
+        <v>3.2679</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.031799999999999</v>
+        <v>4.137</v>
       </c>
       <c r="G6" t="n">
-        <v>32.2746</v>
+        <v>-4.2803</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0315</v>
+        <v>-12.3991</v>
       </c>
       <c r="I6" t="n">
-        <v>33.3062</v>
+        <v>8.1188</v>
       </c>
       <c r="J6" t="n">
-        <v>62.2445</v>
+        <v>23.8739</v>
       </c>
       <c r="K6" t="n">
-        <v>23.7128</v>
+        <v>13.0987</v>
       </c>
       <c r="L6" t="n">
-        <v>38.532</v>
+        <v>10.7754</v>
       </c>
       <c r="M6" t="n">
-        <v>-29.9698</v>
+        <v>-28.1542</v>
       </c>
       <c r="N6" t="n">
-        <v>-24.744</v>
+        <v>-25.4978</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.2256</v>
+        <v>-2.6564</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.1804</v>
+        <v>-5.3522</v>
       </c>
       <c r="Q6" t="n">
-        <v>-44.2035</v>
+        <v>-47.3749</v>
       </c>
       <c r="R6" t="n">
-        <v>42.0236</v>
+        <v>42.0235</v>
       </c>
       <c r="S6" t="n">
-        <v>-22.8752</v>
+        <v>14.288</v>
       </c>
       <c r="T6" t="n">
-        <v>-15.0985</v>
+        <v>6.7862</v>
       </c>
       <c r="U6" t="n">
-        <v>-7.7767</v>
+        <v>7.5015</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.645</v>
+        <v>2.7495</v>
       </c>
       <c r="W6" t="n">
-        <v>11.6638</v>
+        <v>19.9828</v>
       </c>
       <c r="X6" t="n">
-        <v>-12.3087</v>
+        <v>-17.2337</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>D. SHERIFF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>6.120200000000001</v>
+        <v>7.1628</v>
       </c>
       <c r="E7" t="n">
-        <v>8.040600000000001</v>
+        <v>3.380999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.920400000000001</v>
+        <v>3.7817</v>
       </c>
       <c r="G7" t="n">
-        <v>-7.256</v>
+        <v>-1.540399999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-6.471499999999999</v>
+        <v>-8.1022</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7843999999999991</v>
+        <v>6.5618</v>
       </c>
       <c r="J7" t="n">
-        <v>25.2594</v>
+        <v>11.0265</v>
       </c>
       <c r="K7" t="n">
-        <v>21.6446</v>
+        <v>4.835299999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>3.6151</v>
+        <v>6.1914</v>
       </c>
       <c r="M7" t="n">
-        <v>-32.5157</v>
+        <v>-12.5666</v>
       </c>
       <c r="N7" t="n">
-        <v>-28.1163</v>
+        <v>-12.9372</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.399</v>
+        <v>0.3707000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>21.2099</v>
+        <v>-0.1984000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-28.9402</v>
+        <v>-36.6709</v>
       </c>
       <c r="R7" t="n">
-        <v>50.1506</v>
+        <v>36.4732</v>
       </c>
       <c r="S7" t="n">
-        <v>-12.2436</v>
+        <v>10.2995</v>
       </c>
       <c r="T7" t="n">
-        <v>-7.5618</v>
+        <v>6.8804</v>
       </c>
       <c r="U7" t="n">
-        <v>-4.6822</v>
+        <v>3.4191</v>
       </c>
       <c r="V7" t="n">
-        <v>4.4098</v>
+        <v>-1.398299999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>19.2839</v>
+        <v>22.1455</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.8737</v>
+        <v>-23.5436</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9251</v>
+        <v>5.424200000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>7.6067</v>
+        <v>10.5571</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.6814</v>
+        <v>-5.1328</v>
       </c>
       <c r="G8" t="n">
         <v>-4.696599999999999</v>
@@ -1078,13 +1078,13 @@
         <v>44.0058</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1945</v>
+        <v>2.3047</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.9938</v>
+        <v>0.9563000000000003</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7994000000000002</v>
+        <v>1.3478</v>
       </c>
       <c r="V8" t="n">
         <v>-3.8789</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. CHEKRI KOURAYCHE</t>
+          <t>A. LIMON LIMON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5960999999999972</v>
+        <v>-0.4366999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0632</v>
+        <v>-1.4219</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.467400000000001</v>
+        <v>0.9851000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>21.886</v>
+        <v>-0.7351000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>18.102</v>
+        <v>-0.3889</v>
       </c>
       <c r="I9" t="n">
-        <v>3.784399999999999</v>
+        <v>-0.3463</v>
       </c>
       <c r="J9" t="n">
-        <v>47.5569</v>
+        <v>-0.5544</v>
       </c>
       <c r="K9" t="n">
-        <v>41.2747</v>
+        <v>-0.5985</v>
       </c>
       <c r="L9" t="n">
-        <v>6.282200000000001</v>
+        <v>0.0441</v>
       </c>
       <c r="M9" t="n">
-        <v>-25.671</v>
+        <v>-0.1808</v>
       </c>
       <c r="N9" t="n">
-        <v>-23.173</v>
+        <v>0.2096000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4977</v>
+        <v>-0.3903</v>
       </c>
       <c r="P9" t="n">
-        <v>-53.3218</v>
+        <v>0.9911</v>
       </c>
       <c r="Q9" t="n">
-        <v>-101.6885</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>48.3663</v>
+        <v>0.9911</v>
       </c>
       <c r="S9" t="n">
-        <v>42.2402</v>
+        <v>0.2478</v>
       </c>
       <c r="T9" t="n">
-        <v>30.3517</v>
+        <v>-0.1936</v>
       </c>
       <c r="U9" t="n">
-        <v>11.8883</v>
+        <v>0.4414</v>
       </c>
       <c r="V9" t="n">
-        <v>-10.2079</v>
+        <v>-0.9405</v>
       </c>
       <c r="W9" t="n">
-        <v>26.8436</v>
+        <v>-0.674</v>
       </c>
       <c r="X9" t="n">
-        <v>-37.0516</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. LIMON LIMON</t>
+          <t>A. MARTIN BONNEMAISON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7143</v>
+        <v>-3.3914</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7275</v>
+        <v>-4.1698</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0133</v>
+        <v>0.7786000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7351000000000001</v>
+        <v>1.4848</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3889</v>
+        <v>1.377899999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3463</v>
+        <v>0.1070000000000003</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5544</v>
+        <v>2.0556</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5985</v>
+        <v>2.4018</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0441</v>
+        <v>-0.3460000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1808</v>
+        <v>-0.5707999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2096000000000001</v>
+        <v>-1.0239</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3903</v>
+        <v>0.4529000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9911</v>
+        <v>-1.784</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.9555</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9911</v>
+        <v>3.1715</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02980000000000002</v>
+        <v>-1.686</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4992</v>
+        <v>-0.9329000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4694</v>
+        <v>-0.7530000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9405</v>
+        <v>-1.4063</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.674</v>
+        <v>-0.337</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2666</v>
+        <v>-1.0693</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MARTIN BONNEMAISON</t>
+          <t>D. MALAVE FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3233</v>
+        <v>-7.343499999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.866400000000001</v>
+        <v>-7.1449</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4567000000000002</v>
+        <v>-0.1986000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4848</v>
+        <v>0.4325999999999994</v>
       </c>
       <c r="H11" t="n">
-        <v>1.377899999999999</v>
+        <v>-2.6902</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1070000000000003</v>
+        <v>3.1226</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0556</v>
+        <v>3.4096</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4018</v>
+        <v>1.7365</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3460000000000001</v>
+        <v>1.6732</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5707999999999999</v>
+        <v>-2.977</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0239</v>
+        <v>-4.4266</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4529000000000001</v>
+        <v>1.4495</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.784</v>
+        <v>-2.3788</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.9555</v>
+        <v>-10.9021</v>
       </c>
       <c r="R11" t="n">
-        <v>3.1715</v>
+        <v>8.523400000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.6179</v>
+        <v>-0.4631999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6297</v>
+        <v>-0.3113</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.9882</v>
+        <v>-0.1521000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4063</v>
+        <v>-4.9341</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.337</v>
+        <v>0.6588999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0693</v>
+        <v>-5.5929</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. MALAVE FERNANDEZ</t>
+          <t>T. LIBERATORE DARGAM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.5324</v>
+        <v>-10.1615</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.929</v>
+        <v>-2.422</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6031</v>
+        <v>-7.7398</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4325999999999994</v>
+        <v>-11.1277</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.6902</v>
+        <v>-11.6221</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1226</v>
+        <v>0.4941999999999998</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4096</v>
+        <v>-1.8184</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7365</v>
+        <v>-2.1359</v>
       </c>
       <c r="L12" t="n">
-        <v>1.6732</v>
+        <v>0.3174999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.977</v>
+        <v>-9.309200000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.4266</v>
+        <v>-9.485800000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4495</v>
+        <v>0.1766999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.3788</v>
+        <v>13.4791</v>
       </c>
       <c r="Q12" t="n">
-        <v>-10.9021</v>
+        <v>-6.1448</v>
       </c>
       <c r="R12" t="n">
-        <v>8.523400000000001</v>
+        <v>19.6239</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.652</v>
+        <v>3.1792</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.0956</v>
+        <v>3.0015</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5566</v>
+        <v>0.1777000000000002</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.9341</v>
+        <v>-15.6923</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6588999999999999</v>
+        <v>2.54</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.5929</v>
+        <v>-18.2323</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. LIBERATORE DARGAM</t>
+          <t>F. CHEKRI KOURAYCHE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.2042</v>
+        <v>-18.5279</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.1144</v>
+        <v>-11.5409</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.0898</v>
+        <v>-6.986499999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.1277</v>
+        <v>21.886</v>
       </c>
       <c r="H13" t="n">
-        <v>-11.6221</v>
+        <v>18.102</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4941999999999998</v>
+        <v>3.784399999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.8184</v>
+        <v>47.5569</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.1359</v>
+        <v>41.2747</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3174999999999999</v>
+        <v>6.282200000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.309200000000001</v>
+        <v>-25.671</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.485800000000001</v>
+        <v>-23.173</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1766999999999999</v>
+        <v>-2.4977</v>
       </c>
       <c r="P13" t="n">
-        <v>13.4791</v>
+        <v>-53.3218</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.1448</v>
+        <v>-101.6885</v>
       </c>
       <c r="R13" t="n">
-        <v>19.6239</v>
+        <v>48.3663</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.8631</v>
+        <v>23.1163</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.691</v>
+        <v>15.7472</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.1723</v>
+        <v>7.3692</v>
       </c>
       <c r="V13" t="n">
-        <v>-15.6923</v>
+        <v>-10.2079</v>
       </c>
       <c r="W13" t="n">
-        <v>2.54</v>
+        <v>26.8436</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.2323</v>
+        <v>-37.0516</v>
       </c>
     </row>
     <row r="14">
@@ -1501,16 +1501,16 @@
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>142.1336</v>
+        <v>143.9638</v>
       </c>
       <c r="E14" t="n">
-        <v>136.7774</v>
+        <v>132.4141</v>
       </c>
       <c r="F14" t="n">
-        <v>5.356100000000003</v>
+        <v>11.5498</v>
       </c>
       <c r="G14" t="n">
-        <v>65.46799999999999</v>
+        <v>65.46800000000002</v>
       </c>
       <c r="H14" t="n">
         <v>2.919100000000004</v>
@@ -1519,13 +1519,13 @@
         <v>62.55</v>
       </c>
       <c r="J14" t="n">
-        <v>312.4746000000001</v>
+        <v>312.4746</v>
       </c>
       <c r="K14" t="n">
         <v>226.2942</v>
       </c>
       <c r="L14" t="n">
-        <v>86.18169999999998</v>
+        <v>86.18169999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-247.006</v>
@@ -1537,7 +1537,7 @@
         <v>-23.6297</v>
       </c>
       <c r="P14" t="n">
-        <v>19.0292</v>
+        <v>19.02920000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-393.8665</v>
@@ -1546,13 +1546,13 @@
         <v>412.8993</v>
       </c>
       <c r="S14" t="n">
-        <v>74.95110000000001</v>
+        <v>76.7811</v>
       </c>
       <c r="T14" t="n">
-        <v>58.0487</v>
+        <v>53.68499999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>16.901</v>
+        <v>23.0951</v>
       </c>
       <c r="V14" t="n">
         <v>-17.3146</v>
